--- a/To-Do-List.xlsx
+++ b/To-Do-List.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0890a8acb5f6bac5/Bureau/Dossier/IMSD/To_do_list/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42711BC-0392-4465-A53E-C7C204F5D4DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675D9A95-FABE-440D-A701-95A0D9701450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="61">
   <si>
     <t>TO-DO LIST</t>
   </si>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t>Ajouter les nouvelles procédures</t>
-  </si>
-  <si>
-    <t>En attente</t>
   </si>
 </sst>
 </file>
@@ -231,7 +228,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,120 +237,140 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="28"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFE8B84B"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FFDAAC44"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="8.5"/>
+      <color rgb="FFDAAC44"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8.5"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="9"/>
-      <color rgb="FF1B2A4A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF131934"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
-      <color rgb="FF1B2A4A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFE8B84B"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FFDAAC44"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF131934"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9.5"/>
+      <color rgb="FF666666"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF1B2A4A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FFC8893A"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7.5"/>
+      <color rgb="FF131934"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color rgb="FF555555"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFC99A2E"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF1B2A4A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FFC0392B"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFB8763A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF3F7E4F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFC0504D"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF3F8A5F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF4F8A5B"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="8.5"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,72 +379,126 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B2A4A"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="FF131934"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC0504D"/>
-        <bgColor rgb="FFB8763A"/>
+        <fgColor rgb="FFDAAC44"/>
+        <bgColor rgb="FFE89B2E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB8763A"/>
-        <bgColor rgb="FFC99A2E"/>
+        <fgColor rgb="FFA9372C"/>
+        <bgColor rgb="FFC0392B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4F8A5B"/>
-        <bgColor rgb="FF808080"/>
+        <fgColor rgb="FFB9772B"/>
+        <bgColor rgb="FFC8893A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF6E0"/>
-        <bgColor rgb="FFF4F7FB"/>
+        <fgColor rgb="FF3F7E4F"/>
+        <bgColor rgb="FF3F8A5F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8B84B"/>
-        <bgColor rgb="FFC99A2E"/>
+        <fgColor rgb="FFEFF5FF"/>
+        <bgColor rgb="FFEAEDFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF4F7FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE9D2"/>
-        <bgColor rgb="FFFFF6E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4F7FB"/>
+        <fgColor rgb="FFFDFCFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDCE9D8"/>
-        <bgColor rgb="FFF2DCDB"/>
+        <fgColor rgb="FFC69737"/>
+        <bgColor rgb="FFC8893A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2DCDB"/>
-        <bgColor rgb="FFFCE9D2"/>
+        <fgColor rgb="FFFDF4E7"/>
+        <bgColor rgb="FFFDFCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAEDFC"/>
+        <bgColor rgb="FFE5F1ED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0602C"/>
+        <bgColor rgb="FFD46A2C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3F8A5F"/>
+        <bgColor rgb="FF3F7E4F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5F1ED"/>
+        <bgColor rgb="FFEAEDFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0392B"/>
+        <bgColor rgb="FFA9372C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF939246"/>
+        <bgColor rgb="FFA49441"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD56D2C"/>
+        <bgColor rgb="FFD46A2C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD46A2C"/>
+        <bgColor rgb="FFD56D2C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE89B2E"/>
+        <bgColor rgb="FFDAAC44"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC84C2B"/>
+        <bgColor rgb="FFC0392B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -437,29 +508,133 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right/>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -467,125 +642,786 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="13" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="21" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="85">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEAEDFC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFDFCFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC84C2B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFD8732C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE89B2E"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA49441"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608D55"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC0392B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFD0602C"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -594,19 +1430,19 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFB8763A"/>
+      <rgbColor rgb="FFA49441"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FFC0504D"/>
-      <rgbColor rgb="FFFFF6E0"/>
-      <rgbColor rgb="FFF4F7FB"/>
+      <rgbColor rgb="FF3F7E4F"/>
+      <rgbColor rgb="FFB9772B"/>
+      <rgbColor rgb="FF608D55"/>
+      <rgbColor rgb="FFADA5F0"/>
+      <rgbColor rgb="FFC0392B"/>
+      <rgbColor rgb="FFFDF4E7"/>
+      <rgbColor rgb="FFE5F1ED"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFC8893A"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -616,29 +1452,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFDCE9D8"/>
-      <rgbColor rgb="FFFCE9D2"/>
+      <rgbColor rgb="FFEFF5FF"/>
+      <rgbColor rgb="FFEAEDFC"/>
+      <rgbColor rgb="FFFDFCFF"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF2DCDB"/>
+      <rgbColor rgb="FFD56D2C"/>
+      <rgbColor rgb="FFD46A2C"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFE8B84B"/>
-      <rgbColor rgb="FFC99A2E"/>
-      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FFC69737"/>
+      <rgbColor rgb="FFDAAC44"/>
+      <rgbColor rgb="FFE89B2E"/>
+      <rgbColor rgb="FFD8732C"/>
+      <rgbColor rgb="FF666666"/>
+      <rgbColor rgb="FF939246"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF3F8A5F"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FFA9372C"/>
+      <rgbColor rgb="FFC84C2B"/>
       <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF4F8A5B"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF444444"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1B2A4A"/>
+      <rgbColor rgb="FF131934"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
       <rgbColor rgb="00003300"/>
@@ -840,797 +1676,1236 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <tabColor rgb="FF1B2A4A"/>
+    <tabColor rgb="FF131934"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T28"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="5" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="38" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="1" max="1" width="11" style="3" customWidth="1"/>
+    <col min="2" max="2" width="5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28" style="3" customWidth="1"/>
+    <col min="4" max="4" width="14" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7" style="3" customWidth="1"/>
+    <col min="7" max="7" width="4.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="6.1796875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="4.26953125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="5.36328125" style="3" customWidth="1"/>
+    <col min="11" max="17" width="4.26953125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="9.1796875" style="3" customWidth="1"/>
+    <col min="19" max="19" width="32" style="3" customWidth="1"/>
+    <col min="20" max="20" width="12" style="3" customWidth="1"/>
+    <col min="21" max="16384" width="8.6328125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24"/>
-      <c r="B1" s="25" t="s">
+    <row r="1" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="24"/>
-      <c r="B3" s="26" t="s">
+    <row r="3" spans="1:20" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="26"/>
+    <row r="4" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
     </row>
-    <row r="6" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+    <row r="5" spans="1:20" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+    </row>
+    <row r="6" spans="1:20" ht="3.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27" t="s">
+      <c r="B7" s="65"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28" t="s">
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="29" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30" t="s">
+      <c r="J7" s="8"/>
+      <c r="K7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="30"/>
-      <c r="K6" s="31" t="s">
+      <c r="L7" s="9"/>
+      <c r="M7" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32" t="s">
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="32"/>
+      <c r="T7" s="70"/>
     </row>
-    <row r="7" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
+    <row r="8" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="67"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="55"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="57"/>
+      <c r="S8" s="70"/>
+      <c r="T8" s="70"/>
     </row>
-    <row r="8" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="33">
+    <row r="9" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="58">
         <f ca="1">TODAY()</f>
         <v>46200</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="34">
-        <f>COUNTA(C13:C200)</f>
+      <c r="B9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="10">
+        <f>COUNTA(C14:C200)</f>
         <v>15</v>
       </c>
-      <c r="D8" s="34"/>
-      <c r="E8" s="35">
-        <f>COUNTIF(N13:N200,"En attente")</f>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="11">
+        <f>COUNTIF(T14:T200,"En attente")</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12">
+        <f>COUNTIF(T14:T200,"En cours")</f>
+        <v>11</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="13">
+        <f>COUNTIF(T14:T200,"Terminé")</f>
+        <v>4</v>
+      </c>
+      <c r="L9" s="13"/>
+      <c r="M9" s="55"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="56"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="57"/>
+      <c r="S9" s="71">
+        <f>IFERROR(AVERAGE(F14:F200),0)</f>
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="T9" s="71"/>
+    </row>
+    <row r="10" spans="1:20" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="55"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="57"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="71"/>
+    </row>
+    <row r="11" spans="1:20" ht="3.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+    </row>
+    <row r="12" spans="1:20" ht="3.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="T13" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16">
         <v>1</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35">
-        <f>COUNTIF(N13:N200,"En cours")</f>
-        <v>10</v>
-      </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35">
-        <f>COUNTIF(N13:N200,"Terminé")</f>
-        <v>4</v>
-      </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="36">
-        <f>IFERROR(AVERAGE(F13:F200),0)</f>
-        <v>0.51133333333333331</v>
-      </c>
-      <c r="N8" s="36"/>
-    </row>
-    <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-    </row>
-    <row r="10" spans="1:14" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="19">
+      <c r="B14" s="16"/>
+      <c r="C14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="20">
         <v>1</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="G13" s="20">
-        <v>0.6</v>
-      </c>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
-      <c r="M13" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="21">
-        <v>2</v>
-      </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="G14" s="22">
-        <v>0.2</v>
-      </c>
+      <c r="G14" s="21"/>
       <c r="H14" s="22"/>
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="22"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="24">
+        <f t="shared" ref="R14:R28" si="0">F14</f>
+        <v>1</v>
+      </c>
+      <c r="S14" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="T14" s="26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="27">
+        <v>2</v>
+      </c>
+      <c r="B15" s="27"/>
+      <c r="C15" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="31">
+        <v>0.2</v>
+      </c>
+      <c r="G15" s="32"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="35">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="S15" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="T15" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19">
+    <row r="16" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16">
         <v>3</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="2" t="s">
+      <c r="B16" s="16"/>
+      <c r="C16" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D16" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E16" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F16" s="20">
         <v>1</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G16" s="37"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="39">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="6" t="s">
+      <c r="S16" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="T16" s="40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="21">
+    <row r="17" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
         <v>4</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="8" t="s">
+      <c r="B17" s="27"/>
+      <c r="C17" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D17" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E17" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F17" s="31">
         <v>0</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G17" s="42"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="35">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="12" t="s">
+      <c r="S17" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="T17" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="19">
+    <row r="18" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
         <v>5</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="2" t="s">
+      <c r="B18" s="16"/>
+      <c r="C18" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D18" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E18" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F18" s="20">
         <v>0.75</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G18" s="44"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="45"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="45"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="24">
+        <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="6" t="s">
+      <c r="S18" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="N17" s="7" t="s">
+      <c r="T18" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="21">
+    <row r="19" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
         <v>6</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="8" t="s">
+      <c r="B19" s="27"/>
+      <c r="C19" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D19" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E19" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F19" s="31">
         <v>0.27</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G19" s="46"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="35">
+        <f t="shared" si="0"/>
         <v>0.27</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="12" t="s">
+      <c r="S19" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="N18" s="7" t="s">
+      <c r="T19" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="19">
+    <row r="20" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="16">
         <v>7</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="2" t="s">
+      <c r="B20" s="16"/>
+      <c r="C20" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D20" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E20" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F20" s="20">
         <v>1</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G20" s="37"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="38"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="38"/>
+      <c r="R20" s="39">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="6" t="s">
+      <c r="S20" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="N19" s="13" t="s">
+      <c r="T20" s="40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="21">
+    <row r="21" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27">
         <v>8</v>
       </c>
-      <c r="B20" s="21"/>
-      <c r="C20" s="8" t="s">
+      <c r="B21" s="27"/>
+      <c r="C21" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E21" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F21" s="31">
         <v>0.25</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G21" s="49"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="35">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="12" t="s">
+      <c r="S21" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="N20" s="7" t="s">
+      <c r="T21" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="19">
+    <row r="22" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="16">
         <v>9</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="2" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E22" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F22" s="20">
         <v>0.5</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G22" s="51"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="24">
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="6" t="s">
+      <c r="S22" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="N21" s="7" t="s">
+      <c r="T22" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="21">
+    <row r="23" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="27">
         <v>10</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="8" t="s">
+      <c r="B23" s="27"/>
+      <c r="C23" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D23" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E23" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F23" s="31">
         <v>0.5</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G23" s="51"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="35">
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="12" t="s">
+      <c r="S23" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="7" t="s">
+      <c r="T23" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="19">
+    <row r="24" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
         <v>11</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="2" t="s">
+      <c r="B24" s="16"/>
+      <c r="C24" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E24" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F24" s="20">
         <v>0.25</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G24" s="49"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="24">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="6" t="s">
+      <c r="S24" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="N23" s="7" t="s">
+      <c r="T24" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="21">
+    <row r="25" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="27">
         <v>12</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="8" t="s">
+      <c r="B25" s="27"/>
+      <c r="C25" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D25" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E25" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F25" s="31">
         <v>1</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G25" s="37"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="38"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="38"/>
+      <c r="R25" s="39">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="12" t="s">
+      <c r="S25" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="N24" s="13" t="s">
+      <c r="T25" s="40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="19">
+    <row r="26" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
         <v>13</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="2" t="s">
+      <c r="B26" s="16"/>
+      <c r="C26" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D26" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E26" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F26" s="20">
         <v>1</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G26" s="37"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="38"/>
+      <c r="R26" s="39">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="6" t="s">
+      <c r="S26" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="N25" s="13" t="s">
+      <c r="T26" s="40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="21">
+    <row r="27" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="27">
         <v>14</v>
       </c>
-      <c r="B26" s="21"/>
-      <c r="C26" s="8" t="s">
+      <c r="B27" s="27"/>
+      <c r="C27" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D27" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E27" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F27" s="31">
         <v>0.25</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G27" s="49"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="35">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="12" t="s">
+      <c r="S27" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="N26" s="7" t="s">
+      <c r="T27" s="26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="19">
+    <row r="28" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="16">
         <v>15</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="2" t="s">
+      <c r="B28" s="16"/>
+      <c r="C28" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D28" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E28" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F28" s="20">
         <v>0.1</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G28" s="54"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+      <c r="L28" s="23"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="23"/>
+      <c r="O28" s="23"/>
+      <c r="P28" s="23"/>
+      <c r="Q28" s="23"/>
+      <c r="R28" s="24">
+        <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="6" t="s">
+      <c r="S28" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="N27" s="18" t="s">
-        <v>61</v>
+      <c r="T28" s="26" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="33">
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M7:R10"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="G13:R13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A1:A4"/>
-    <mergeCell ref="B1:N2"/>
-    <mergeCell ref="B3:N4"/>
-    <mergeCell ref="A6:B7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="E6:F7"/>
-    <mergeCell ref="G6:H7"/>
-    <mergeCell ref="I6:J7"/>
-    <mergeCell ref="K6:L9"/>
-    <mergeCell ref="M6:N7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="I8:J9"/>
-    <mergeCell ref="M8:N9"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="G12:L12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="G13:L13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="G14:L14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="G15:L15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G17:L17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="G20:L20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="G21:L21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:L22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="G23:L23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="G27:L27"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="G24:L24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="G25:L25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="G26:L26"/>
+    <mergeCell ref="B1:T2"/>
+    <mergeCell ref="B3:T4"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="G7:H8"/>
+    <mergeCell ref="I7:J8"/>
+    <mergeCell ref="K7:L8"/>
+    <mergeCell ref="S7:T8"/>
+    <mergeCell ref="A9:C10"/>
+    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="G9:H10"/>
+    <mergeCell ref="I9:J10"/>
+    <mergeCell ref="K9:L10"/>
+    <mergeCell ref="S9:T10"/>
   </mergeCells>
-  <conditionalFormatting sqref="G13:G27">
-    <cfRule type="dataBar" priority="2">
-      <dataBar>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="1"/>
-        <color rgb="FF5FA8A0"/>
-      </dataBar>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1CFC7CF4-ECC9-49E5-BBCE-3FABAC78118B}</x14:id>
-        </ext>
-      </extLst>
+  <conditionalFormatting sqref="G14:G28">
+    <cfRule type="expression" dxfId="84" priority="2">
+      <formula>$F14&lt;0.0833333333333333</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="3">
+      <formula>AND($F14&gt;=(0.0833333333333333-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="4">
+      <formula>AND($F14&gt;=(0.0833333333333333-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="5">
+      <formula>AND($F14&gt;=(0.0833333333333333-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="6">
+      <formula>AND($F14&gt;=(0.0833333333333333-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="79" priority="7">
+      <formula>AND($F14&gt;=(0.0833333333333333-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="8">
+      <formula>AND($F14&lt;0.0833333333333333,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="9">
+      <formula>AND($F14&lt;0.0833333333333333,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14:H28">
+    <cfRule type="expression" dxfId="76" priority="10">
+      <formula>AND($F14&gt;=(0.166666666666667-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="11">
+      <formula>AND($F14&gt;=(0.166666666666667-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="12">
+      <formula>AND($F14&gt;=(0.166666666666667-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="13">
+      <formula>AND($F14&gt;=(0.166666666666667-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="14">
+      <formula>AND($F14&gt;=(0.166666666666667-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="15">
+      <formula>AND($F14&lt;0.166666666666667,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="16">
+      <formula>AND($F14&lt;0.166666666666667,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I14:I28">
+    <cfRule type="expression" dxfId="69" priority="17">
+      <formula>AND($F14&gt;=(0.25-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="18">
+      <formula>AND($F14&gt;=(0.25-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="19">
+      <formula>AND($F14&gt;=(0.25-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="20">
+      <formula>AND($F14&gt;=(0.25-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="21">
+      <formula>AND($F14&gt;=(0.25-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="22">
+      <formula>AND($F14&lt;0.25,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="23">
+      <formula>AND($F14&lt;0.25,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J14:J28">
+    <cfRule type="expression" dxfId="62" priority="24">
+      <formula>AND($F14&gt;=(0.333333333333333-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="25">
+      <formula>AND($F14&gt;=(0.333333333333333-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="26">
+      <formula>AND($F14&gt;=(0.333333333333333-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="27">
+      <formula>AND($F14&gt;=(0.333333333333333-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="28">
+      <formula>AND($F14&gt;=(0.333333333333333-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="29">
+      <formula>AND($F14&lt;0.333333333333333,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="30">
+      <formula>AND($F14&lt;0.333333333333333,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K14:K28">
+    <cfRule type="expression" dxfId="55" priority="31">
+      <formula>AND($F14&gt;=(0.416666666666667-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="32">
+      <formula>AND($F14&gt;=(0.416666666666667-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="33">
+      <formula>AND($F14&gt;=(0.416666666666667-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="34">
+      <formula>AND($F14&gt;=(0.416666666666667-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="35">
+      <formula>AND($F14&gt;=(0.416666666666667-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="36">
+      <formula>AND($F14&lt;0.416666666666667,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="37">
+      <formula>AND($F14&lt;0.416666666666667,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L14:L28">
+    <cfRule type="expression" dxfId="48" priority="38">
+      <formula>AND($F14&gt;=(0.5-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="39">
+      <formula>AND($F14&gt;=(0.5-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="40">
+      <formula>AND($F14&gt;=(0.5-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="41">
+      <formula>AND($F14&gt;=(0.5-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="42">
+      <formula>AND($F14&gt;=(0.5-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="43">
+      <formula>AND($F14&lt;0.5,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="44">
+      <formula>AND($F14&lt;0.5,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M14:M28">
+    <cfRule type="expression" dxfId="41" priority="45">
+      <formula>AND($F14&gt;=(0.583333333333333-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="46">
+      <formula>AND($F14&gt;=(0.583333333333333-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="47">
+      <formula>AND($F14&gt;=(0.583333333333333-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="48">
+      <formula>AND($F14&gt;=(0.583333333333333-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="49">
+      <formula>AND($F14&gt;=(0.583333333333333-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="50">
+      <formula>AND($F14&lt;0.583333333333333,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="51">
+      <formula>AND($F14&lt;0.583333333333333,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N14:N28">
+    <cfRule type="expression" dxfId="34" priority="52">
+      <formula>AND($F14&gt;=(0.666666666666667-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="53">
+      <formula>AND($F14&gt;=(0.666666666666667-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="54">
+      <formula>AND($F14&gt;=(0.666666666666667-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="55">
+      <formula>AND($F14&gt;=(0.666666666666667-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="56">
+      <formula>AND($F14&gt;=(0.666666666666667-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="57">
+      <formula>AND($F14&lt;0.666666666666667,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="58">
+      <formula>AND($F14&lt;0.666666666666667,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O14:O28">
+    <cfRule type="expression" dxfId="27" priority="59">
+      <formula>AND($F14&gt;=(0.75-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="60">
+      <formula>AND($F14&gt;=(0.75-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="61">
+      <formula>AND($F14&gt;=(0.75-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="62">
+      <formula>AND($F14&gt;=(0.75-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="63">
+      <formula>AND($F14&gt;=(0.75-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="64">
+      <formula>AND($F14&lt;0.75,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="65">
+      <formula>AND($F14&lt;0.75,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P14:P28">
+    <cfRule type="expression" dxfId="20" priority="66">
+      <formula>AND($F14&gt;=(0.833333333333333-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="67">
+      <formula>AND($F14&gt;=(0.833333333333333-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="68">
+      <formula>AND($F14&gt;=(0.833333333333333-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="69">
+      <formula>AND($F14&gt;=(0.833333333333333-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="70">
+      <formula>AND($F14&gt;=(0.833333333333333-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="71">
+      <formula>AND($F14&lt;0.833333333333333,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="72">
+      <formula>AND($F14&lt;0.833333333333333,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q14:Q28">
+    <cfRule type="expression" dxfId="13" priority="73">
+      <formula>AND($F14&gt;=(0.916666666666667-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="74">
+      <formula>AND($F14&gt;=(0.916666666666667-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="75">
+      <formula>AND($F14&gt;=(0.916666666666667-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="76">
+      <formula>AND($F14&gt;=(0.916666666666667-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="77">
+      <formula>AND($F14&gt;=(0.916666666666667-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="78">
+      <formula>AND($F14&lt;0.916666666666667,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="79">
+      <formula>AND($F14&lt;0.916666666666667,MOD(ROW()-14,2)=1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R14:R28">
+    <cfRule type="expression" dxfId="6" priority="80">
+      <formula>AND($F14&gt;=(1-0.0001),$F14&gt;=0.8-0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="81">
+      <formula>AND($F14&gt;=(1-0.0001),$F14&gt;=0.6-0.0001,$F14&lt;0.8+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="82">
+      <formula>AND($F14&gt;=(1-0.0001),$F14&gt;=0.4-0.0001,$F14&lt;0.6+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="83">
+      <formula>AND($F14&gt;=(1-0.0001),$F14&gt;=0.2-0.0001,$F14&lt;0.4+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="84">
+      <formula>AND($F14&gt;=(1-0.0001),$F14&gt;=0-0.0001,$F14&lt;0.2+0.0001)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="85">
+      <formula>AND($F14&lt;1,MOD(ROW()-14,2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="86">
+      <formula>AND($F14&lt;1,MOD(ROW()-14,2)=1)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="N13:N37" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="T14:T38" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"En attente,En cours,Terminé"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E13:E37" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E14:E38" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Haute,Moyenne,Basse"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1CFC7CF4-ECC9-49E5-BBCE-3FABAC78118B}">
-            <x14:dataBar axisPosition="none">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-              <x14:negativeFillColor rgb="FF5FA8A0"/>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>G13:G27</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>